--- a/fundraiser_forms/010_nonprofit_donation_form--fundraiser_forms.xlsx
+++ b/fundraiser_forms/010_nonprofit_donation_form--fundraiser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'one-time',_'label':_'one-time'}</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'One-time', 'label': 'One-time'}</t>
+          <t>One-time</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'annually',_'label':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Annually', 'label': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'campaign_1',_'label':_'campaign_1'}</t>
+          <t>campaign_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Campaign 1', 'label': 'Campaign 1'}</t>
+          <t>Campaign 1</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'campaign_2',_'label':_'campaign_2'}</t>
+          <t>campaign_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Campaign 2', 'label': 'Campaign 2'}</t>
+          <t>Campaign 2</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'campaign_3',_'label':_'campaign_3'}</t>
+          <t>campaign_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Campaign 3', 'label': 'Campaign 3'}</t>
+          <t>Campaign 3</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'one-time_donations',_'label':_'one-time_donations'}</t>
+          <t>one-time_donations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'One-time Donations', 'label': 'One-time Donations'}</t>
+          <t>One-time Donations</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'recurring_donations_(e.g.,_monthly,_annuity)',_'label':_'recurring_donations_(e.g.,_monthly,_annuity)'}</t>
+          <t>recurring_donations_(e.g.,_monthly,_annuity)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Recurring Donations (e.g., monthly, annuity)', 'label': 'Recurring Donations (e.g., monthly, annuity)'}</t>
+          <t>Recurring Donations (e.g., monthly, annuity)</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'one-time',_'label':_'one-time'}</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'One-time', 'label': 'One-time'}</t>
+          <t>One-time</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'annually',_'label':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Annually', 'label': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
